--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457891</v>
+        <v>113457932</v>
       </c>
       <c r="B2" t="n">
-        <v>56910</v>
+        <v>91302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562941</v>
+        <v>562816</v>
       </c>
       <c r="R2" t="n">
-        <v>6626411</v>
+        <v>6626430</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +772,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosökte och lockade i tallarna. Tillsammans med tofsmes</t>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -1053,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113457897</v>
+        <v>113457891</v>
       </c>
       <c r="B5" t="n">
-        <v>91329</v>
+        <v>56910</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,21 +1065,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1091,26 +1087,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562910</v>
+        <v>562941</v>
       </c>
       <c r="R5" t="n">
-        <v>6626419</v>
+        <v>6626411</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1152,13 +1149,17 @@
           <t>13:30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökte och lockade i tallarna. Tillsammans med tofsmes</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113457932</v>
+        <v>113457897</v>
       </c>
       <c r="B7" t="n">
-        <v>91302</v>
+        <v>91329</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,28 +1304,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1334,14 +1339,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562816</v>
+        <v>562910</v>
       </c>
       <c r="R7" t="n">
-        <v>6626430</v>
+        <v>6626419</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1384,11 +1389,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457932</v>
+        <v>113457901</v>
       </c>
       <c r="B2" t="n">
-        <v>91302</v>
+        <v>91341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -722,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562816</v>
+        <v>562892</v>
       </c>
       <c r="R2" t="n">
-        <v>6626430</v>
+        <v>6626452</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -768,11 +772,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457922</v>
+        <v>113457897</v>
       </c>
       <c r="B3" t="n">
-        <v>91302</v>
+        <v>91341</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,28 +811,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -843,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562843</v>
+        <v>562910</v>
       </c>
       <c r="R3" t="n">
-        <v>6626429</v>
+        <v>6626419</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,11 +896,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457901</v>
+        <v>113457932</v>
       </c>
       <c r="B4" t="n">
-        <v>91329</v>
+        <v>91314</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,32 +935,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -976,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562892</v>
+        <v>562816</v>
       </c>
       <c r="R4" t="n">
-        <v>6626452</v>
+        <v>6626430</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1022,6 +1016,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113457891</v>
+        <v>113457922</v>
       </c>
       <c r="B5" t="n">
-        <v>56910</v>
+        <v>91314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,39 +1060,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1101,13 +1095,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562941</v>
+        <v>562843</v>
       </c>
       <c r="R5" t="n">
-        <v>6626411</v>
+        <v>6626429</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1151,7 +1145,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Födosökte och lockade i tallarna. Tillsammans med tofsmes</t>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,6 +1154,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1181,7 +1176,7 @@
         <v>113457849</v>
       </c>
       <c r="B6" t="n">
-        <v>91329</v>
+        <v>91341</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1292,14 +1287,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113457897</v>
+        <v>113457891</v>
       </c>
       <c r="B7" t="n">
-        <v>91329</v>
+        <v>56911</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1330,26 +1325,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562910</v>
+        <v>562941</v>
       </c>
       <c r="R7" t="n">
-        <v>6626419</v>
+        <v>6626411</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,13 +1387,17 @@
           <t>13:30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökte och lockade i tallarna. Tillsammans med tofsmes</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457901</v>
+        <v>113457932</v>
       </c>
       <c r="B2" t="n">
-        <v>91341</v>
+        <v>91314</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -726,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562892</v>
+        <v>562816</v>
       </c>
       <c r="R2" t="n">
-        <v>6626452</v>
+        <v>6626430</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,6 +768,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -923,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457932</v>
+        <v>113457849</v>
       </c>
       <c r="B4" t="n">
-        <v>91314</v>
+        <v>91341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,28 +936,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -970,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562816</v>
+        <v>562940</v>
       </c>
       <c r="R4" t="n">
-        <v>6626430</v>
+        <v>6626409</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,24 +1008,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1173,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457849</v>
+        <v>113457901</v>
       </c>
       <c r="B6" t="n">
         <v>91341</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1224,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562940</v>
+        <v>562892</v>
       </c>
       <c r="R6" t="n">
-        <v>6626409</v>
+        <v>6626452</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,9 +1247,19 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113457932</v>
       </c>
       <c r="B2" t="n">
-        <v>91314</v>
+        <v>91336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>113457897</v>
       </c>
       <c r="B3" t="n">
-        <v>91341</v>
+        <v>91363</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>113457849</v>
       </c>
       <c r="B4" t="n">
-        <v>91341</v>
+        <v>91363</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>113457922</v>
       </c>
       <c r="B5" t="n">
-        <v>91314</v>
+        <v>91336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>113457901</v>
       </c>
       <c r="B6" t="n">
-        <v>91341</v>
+        <v>91363</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457932</v>
+        <v>113457849</v>
       </c>
       <c r="B2" t="n">
-        <v>91336</v>
+        <v>91367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -722,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562816</v>
+        <v>562940</v>
       </c>
       <c r="R2" t="n">
-        <v>6626430</v>
+        <v>6626409</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,24 +759,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457897</v>
+        <v>113457901</v>
       </c>
       <c r="B3" t="n">
-        <v>91363</v>
+        <v>91367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -847,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562910</v>
+        <v>562892</v>
       </c>
       <c r="R3" t="n">
-        <v>6626419</v>
+        <v>6626452</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -924,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457849</v>
+        <v>113457922</v>
       </c>
       <c r="B4" t="n">
-        <v>91363</v>
+        <v>91340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,32 +925,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -975,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562940</v>
+        <v>562843</v>
       </c>
       <c r="R4" t="n">
-        <v>6626409</v>
+        <v>6626429</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,9 +993,24 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113457922</v>
+        <v>113457897</v>
       </c>
       <c r="B5" t="n">
-        <v>91336</v>
+        <v>91367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,28 +1050,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1081,14 +1085,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562843</v>
+        <v>562910</v>
       </c>
       <c r="R5" t="n">
-        <v>6626429</v>
+        <v>6626419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1131,11 +1135,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457901</v>
+        <v>113457932</v>
       </c>
       <c r="B6" t="n">
-        <v>91363</v>
+        <v>91340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,32 +1174,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1214,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562892</v>
+        <v>562816</v>
       </c>
       <c r="R6" t="n">
-        <v>6626452</v>
+        <v>6626430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1260,6 +1255,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,7 +1290,7 @@
         <v>113457891</v>
       </c>
       <c r="B7" t="n">
-        <v>56911</v>
+        <v>56914</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457849</v>
+        <v>113457922</v>
       </c>
       <c r="B2" t="n">
-        <v>91367</v>
+        <v>91346</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -726,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562940</v>
+        <v>562843</v>
       </c>
       <c r="R2" t="n">
-        <v>6626409</v>
+        <v>6626429</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,9 +755,24 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457901</v>
+        <v>113457932</v>
       </c>
       <c r="B3" t="n">
-        <v>91367</v>
+        <v>91346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,32 +812,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -840,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562892</v>
+        <v>562816</v>
       </c>
       <c r="R3" t="n">
-        <v>6626452</v>
+        <v>6626430</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,6 +893,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457922</v>
+        <v>113457901</v>
       </c>
       <c r="B4" t="n">
-        <v>91340</v>
+        <v>91373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,28 +937,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -960,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562843</v>
+        <v>562892</v>
       </c>
       <c r="R4" t="n">
-        <v>6626429</v>
+        <v>6626452</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,11 +1022,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1052,7 @@
         <v>113457897</v>
       </c>
       <c r="B5" t="n">
-        <v>91367</v>
+        <v>91373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1162,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457932</v>
+        <v>113457849</v>
       </c>
       <c r="B6" t="n">
-        <v>91340</v>
+        <v>91373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,28 +1185,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1209,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562816</v>
+        <v>562940</v>
       </c>
       <c r="R6" t="n">
-        <v>6626430</v>
+        <v>6626409</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,24 +1257,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,7 +1290,7 @@
         <v>113457891</v>
       </c>
       <c r="B7" t="n">
-        <v>56914</v>
+        <v>56918</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457922</v>
+        <v>113457901</v>
       </c>
       <c r="B2" t="n">
-        <v>91346</v>
+        <v>91373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -722,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562843</v>
+        <v>562892</v>
       </c>
       <c r="R2" t="n">
-        <v>6626429</v>
+        <v>6626452</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -768,11 +772,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457932</v>
+        <v>113457849</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>91373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,28 +811,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -847,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562816</v>
+        <v>562940</v>
       </c>
       <c r="R3" t="n">
-        <v>6626430</v>
+        <v>6626409</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,24 +883,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457901</v>
+        <v>113457922</v>
       </c>
       <c r="B4" t="n">
-        <v>91373</v>
+        <v>91346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,32 +925,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -976,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562892</v>
+        <v>562843</v>
       </c>
       <c r="R4" t="n">
-        <v>6626452</v>
+        <v>6626429</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1022,6 +1006,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1173,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457849</v>
+        <v>113457932</v>
       </c>
       <c r="B6" t="n">
-        <v>91373</v>
+        <v>91346</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,32 +1174,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1224,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562940</v>
+        <v>562816</v>
       </c>
       <c r="R6" t="n">
-        <v>6626409</v>
+        <v>6626430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,9 +1242,24 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457901</v>
+        <v>113457849</v>
       </c>
       <c r="B2" t="n">
-        <v>91373</v>
+        <v>91380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562892</v>
+        <v>562940</v>
       </c>
       <c r="R2" t="n">
-        <v>6626452</v>
+        <v>6626409</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,19 +759,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457849</v>
+        <v>113457897</v>
       </c>
       <c r="B3" t="n">
-        <v>91373</v>
+        <v>91380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562940</v>
+        <v>562910</v>
       </c>
       <c r="R3" t="n">
-        <v>6626409</v>
+        <v>6626419</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,9 +873,19 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +916,7 @@
         <v>113457922</v>
       </c>
       <c r="B4" t="n">
-        <v>91346</v>
+        <v>91353</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113457897</v>
+        <v>113457901</v>
       </c>
       <c r="B5" t="n">
-        <v>91373</v>
+        <v>91380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1085,14 +1085,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562910</v>
+        <v>562892</v>
       </c>
       <c r="R5" t="n">
-        <v>6626419</v>
+        <v>6626452</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1165,7 +1165,7 @@
         <v>113457932</v>
       </c>
       <c r="B6" t="n">
-        <v>91346</v>
+        <v>91353</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>113457891</v>
       </c>
       <c r="B7" t="n">
-        <v>56918</v>
+        <v>56925</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457849</v>
+        <v>113457922</v>
       </c>
       <c r="B2" t="n">
-        <v>91380</v>
+        <v>91358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -726,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562940</v>
+        <v>562843</v>
       </c>
       <c r="R2" t="n">
-        <v>6626409</v>
+        <v>6626429</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,9 +755,24 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457897</v>
+        <v>113457849</v>
       </c>
       <c r="B3" t="n">
-        <v>91380</v>
+        <v>91385</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,14 +847,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562910</v>
+        <v>562940</v>
       </c>
       <c r="R3" t="n">
-        <v>6626419</v>
+        <v>6626409</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,19 +884,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457922</v>
+        <v>113457897</v>
       </c>
       <c r="B4" t="n">
-        <v>91353</v>
+        <v>91385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,28 +926,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -956,14 +961,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562843</v>
+        <v>562910</v>
       </c>
       <c r="R4" t="n">
-        <v>6626429</v>
+        <v>6626419</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,11 +1011,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113457901</v>
+        <v>113457932</v>
       </c>
       <c r="B5" t="n">
-        <v>91380</v>
+        <v>91358</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,32 +1050,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1089,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562892</v>
+        <v>562816</v>
       </c>
       <c r="R5" t="n">
-        <v>6626452</v>
+        <v>6626430</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1135,6 +1131,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457932</v>
+        <v>113457901</v>
       </c>
       <c r="B6" t="n">
-        <v>91353</v>
+        <v>91385</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,28 +1175,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1209,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562816</v>
+        <v>562892</v>
       </c>
       <c r="R6" t="n">
-        <v>6626430</v>
+        <v>6626452</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,11 +1260,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,7 +1290,7 @@
         <v>113457891</v>
       </c>
       <c r="B7" t="n">
-        <v>56925</v>
+        <v>56927</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457922</v>
+        <v>113457849</v>
       </c>
       <c r="B2" t="n">
-        <v>91358</v>
+        <v>91413</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -722,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562843</v>
+        <v>562940</v>
       </c>
       <c r="R2" t="n">
-        <v>6626429</v>
+        <v>6626409</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,24 +759,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457849</v>
+        <v>113457901</v>
       </c>
       <c r="B3" t="n">
-        <v>91385</v>
+        <v>91413</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -851,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562940</v>
+        <v>562892</v>
       </c>
       <c r="R3" t="n">
-        <v>6626409</v>
+        <v>6626452</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,9 +873,19 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457897</v>
+        <v>113457922</v>
       </c>
       <c r="B4" t="n">
-        <v>91385</v>
+        <v>91386</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,32 +925,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -961,14 +956,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562910</v>
+        <v>562843</v>
       </c>
       <c r="R4" t="n">
-        <v>6626419</v>
+        <v>6626429</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,6 +1006,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1041,7 @@
         <v>113457932</v>
       </c>
       <c r="B5" t="n">
-        <v>91358</v>
+        <v>91386</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457901</v>
+        <v>113457897</v>
       </c>
       <c r="B6" t="n">
-        <v>91385</v>
+        <v>91413</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1210,14 +1210,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562892</v>
+        <v>562910</v>
       </c>
       <c r="R6" t="n">
-        <v>6626452</v>
+        <v>6626419</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1290,7 +1290,7 @@
         <v>113457891</v>
       </c>
       <c r="B7" t="n">
-        <v>56927</v>
+        <v>56955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457901</v>
+        <v>113457922</v>
       </c>
       <c r="B3" t="n">
-        <v>91413</v>
+        <v>91386</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,32 +801,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -840,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562892</v>
+        <v>562843</v>
       </c>
       <c r="R3" t="n">
-        <v>6626452</v>
+        <v>6626429</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,6 +882,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457922</v>
+        <v>113457897</v>
       </c>
       <c r="B4" t="n">
-        <v>91386</v>
+        <v>91413</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,28 +926,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -956,14 +961,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562843</v>
+        <v>562910</v>
       </c>
       <c r="R4" t="n">
-        <v>6626429</v>
+        <v>6626419</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,11 +1011,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113457932</v>
+        <v>113457901</v>
       </c>
       <c r="B5" t="n">
-        <v>91386</v>
+        <v>91413</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,28 +1050,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1085,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562816</v>
+        <v>562892</v>
       </c>
       <c r="R5" t="n">
-        <v>6626430</v>
+        <v>6626452</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1131,11 +1135,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457897</v>
+        <v>113457932</v>
       </c>
       <c r="B6" t="n">
-        <v>91413</v>
+        <v>91386</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,32 +1174,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1210,14 +1205,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562910</v>
+        <v>562816</v>
       </c>
       <c r="R6" t="n">
-        <v>6626419</v>
+        <v>6626430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1260,6 +1255,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457849</v>
+        <v>113457932</v>
       </c>
       <c r="B2" t="n">
-        <v>91413</v>
+        <v>91390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -726,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562940</v>
+        <v>562816</v>
       </c>
       <c r="R2" t="n">
-        <v>6626409</v>
+        <v>6626430</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,9 +755,24 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457922</v>
+        <v>113457897</v>
       </c>
       <c r="B3" t="n">
-        <v>91386</v>
+        <v>91417</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,28 +812,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -832,14 +847,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562843</v>
+        <v>562910</v>
       </c>
       <c r="R3" t="n">
-        <v>6626429</v>
+        <v>6626419</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,11 +897,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457897</v>
+        <v>113457922</v>
       </c>
       <c r="B4" t="n">
-        <v>91413</v>
+        <v>91390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,32 +936,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -961,14 +967,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562910</v>
+        <v>562843</v>
       </c>
       <c r="R4" t="n">
-        <v>6626419</v>
+        <v>6626429</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,6 +1017,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113457901</v>
+        <v>113457849</v>
       </c>
       <c r="B5" t="n">
-        <v>91413</v>
+        <v>91417</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,7 +1084,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1089,10 +1100,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562892</v>
+        <v>562940</v>
       </c>
       <c r="R5" t="n">
-        <v>6626452</v>
+        <v>6626409</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1122,19 +1133,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457932</v>
+        <v>113457901</v>
       </c>
       <c r="B6" t="n">
-        <v>91386</v>
+        <v>91417</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,28 +1175,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1209,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562816</v>
+        <v>562892</v>
       </c>
       <c r="R6" t="n">
-        <v>6626430</v>
+        <v>6626452</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,11 +1260,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457932</v>
+        <v>113457922</v>
       </c>
       <c r="B2" t="n">
         <v>91390</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562816</v>
+        <v>562843</v>
       </c>
       <c r="R2" t="n">
-        <v>6626430</v>
+        <v>6626429</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113457897</v>
+        <v>113457932</v>
       </c>
       <c r="B3" t="n">
-        <v>91417</v>
+        <v>91390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,32 +812,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -847,14 +843,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562910</v>
+        <v>562816</v>
       </c>
       <c r="R3" t="n">
-        <v>6626419</v>
+        <v>6626430</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,6 +893,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113457922</v>
+        <v>113457901</v>
       </c>
       <c r="B4" t="n">
-        <v>91390</v>
+        <v>91417</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,28 +937,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -971,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562843</v>
+        <v>562892</v>
       </c>
       <c r="R4" t="n">
-        <v>6626429</v>
+        <v>6626452</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1017,11 +1022,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1049,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113457849</v>
+        <v>113457897</v>
       </c>
       <c r="B5" t="n">
         <v>91417</v>
@@ -1096,14 +1096,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562940</v>
+        <v>562910</v>
       </c>
       <c r="R5" t="n">
-        <v>6626409</v>
+        <v>6626419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,9 +1133,19 @@
           <t>2023-10-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1173,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457901</v>
+        <v>113457849</v>
       </c>
       <c r="B6" t="n">
         <v>91417</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1214,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562892</v>
+        <v>562940</v>
       </c>
       <c r="R6" t="n">
-        <v>6626452</v>
+        <v>6626409</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1247,19 +1257,9 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -675,44 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113457897</v>
+        <v>113457922</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -722,14 +713,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brusmossarna, Ramnäs sn, Vstm</t>
+          <t>Brudmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562910</v>
+        <v>562843</v>
       </c>
       <c r="R2" t="n">
-        <v>6626419</v>
+        <v>6626429</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,6 +763,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,12 +798,7 @@
         <v>113457932</v>
       </c>
       <c r="B3" t="n">
-        <v>91601</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,12 +918,7 @@
         <v>113457849</v>
       </c>
       <c r="B4" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,15 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113457901</v>
+        <v>113457897</v>
       </c>
       <c r="B5" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1085,14 +1066,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brudmossarna, Ramnäs sn, Vstm</t>
+          <t>Brusmossarna, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562892</v>
+        <v>562910</v>
       </c>
       <c r="R5" t="n">
-        <v>6626452</v>
+        <v>6626419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1162,40 +1143,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113457922</v>
+        <v>113457901</v>
       </c>
       <c r="B6" t="n">
-        <v>91601</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1209,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562843</v>
+        <v>562892</v>
       </c>
       <c r="R6" t="n">
-        <v>6626429</v>
+        <v>6626452</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,11 +1235,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,12 +1265,7 @@
         <v>113457891</v>
       </c>
       <c r="B7" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49718-2023 artfynd.xlsx
+++ b/artfynd/A 49718-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113457922</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113457932</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113457849</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113457897</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113457901</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,8 +1413,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113457891</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>